--- a/packages/adapter-mn-dli/fixtures/licenses-registrations-sample.xlsx
+++ b/packages/adapter-mn-dli/fixtures/licenses-registrations-sample.xlsx
@@ -11,83 +11,98 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
-  <si>
-    <t>License Number</t>
-  </si>
-  <si>
-    <t>License Type</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="78">
+  <si>
+    <t>Bus_Pers</t>
+  </si>
+  <si>
+    <t>License_Type</t>
+  </si>
+  <si>
+    <t>License_Subtype</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Doing Business As</t>
-  </si>
-  <si>
-    <t>Address Line 1</t>
-  </si>
-  <si>
-    <t>Address Line 2</t>
+    <t>DBA_Name</t>
+  </si>
+  <si>
+    <t>Addr1</t>
+  </si>
+  <si>
+    <t>Addr2</t>
   </si>
   <si>
     <t>City</t>
   </si>
   <si>
-    <t>State</t>
+    <t>St</t>
   </si>
   <si>
     <t>Zip</t>
   </si>
   <si>
-    <t>County</t>
-  </si>
-  <si>
-    <t>Phone</t>
+    <t>Phone_No</t>
+  </si>
+  <si>
+    <t>Email_Address</t>
+  </si>
+  <si>
+    <t>Lic_Number</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Issue Date</t>
-  </si>
-  <si>
-    <t>Expiration Date</t>
-  </si>
-  <si>
-    <t>Discipline Indicator</t>
+    <t>Orig_Date</t>
+  </si>
+  <si>
+    <t>Exp_Date</t>
+  </si>
+  <si>
+    <t>Enforcement_Action</t>
+  </si>
+  <si>
+    <t>Renewal_in_Progress</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>Residential Contractor</t>
+  </si>
+  <si>
+    <t>Residential Building Contractor</t>
+  </si>
+  <si>
+    <t>North Star Builders, LLC</t>
+  </si>
+  <si>
+    <t>North Star</t>
+  </si>
+  <si>
+    <t>100 Lake St</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Minneapolis</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>55401</t>
+  </si>
+  <si>
+    <t>6125550100</t>
   </si>
   <si>
     <t>BC000001</t>
   </si>
   <si>
-    <t>Residential Building Contractor</t>
-  </si>
-  <si>
-    <t>North Star Builders, LLC</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>100 Lake St</t>
-  </si>
-  <si>
-    <t>Minneapolis</t>
-  </si>
-  <si>
-    <t>MN</t>
-  </si>
-  <si>
-    <t>55401</t>
-  </si>
-  <si>
-    <t>Hennepin</t>
-  </si>
-  <si>
-    <t>6125550100</t>
-  </si>
-  <si>
     <t>Issued</t>
   </si>
   <si>
@@ -97,40 +112,37 @@
     <t>12/31/2099</t>
   </si>
   <si>
-    <t>N</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Residential Remodeler</t>
+  </si>
+  <si>
+    <t>Remodel, Renew &amp; Repair LLC</t>
+  </si>
+  <si>
+    <t>Renew Co</t>
+  </si>
+  <si>
+    <t>200 Pine Ave</t>
+  </si>
+  <si>
+    <t>Suite 2</t>
+  </si>
+  <si>
+    <t>Saint Paul</t>
+  </si>
+  <si>
+    <t>55101</t>
+  </si>
+  <si>
+    <t>6515550100</t>
   </si>
   <si>
     <t>RE000002</t>
   </si>
   <si>
-    <t>Residential Remodeler</t>
-  </si>
-  <si>
-    <t>Remodel, Renew &amp; Repair LLC</t>
-  </si>
-  <si>
-    <t>Renew Co</t>
-  </si>
-  <si>
-    <t>200 Pine Ave</t>
-  </si>
-  <si>
-    <t>Suite 2</t>
-  </si>
-  <si>
-    <t>Saint Paul</t>
-  </si>
-  <si>
-    <t>55101</t>
-  </si>
-  <si>
-    <t>Ramsey</t>
-  </si>
-  <si>
-    <t>6515550100</t>
-  </si>
-  <si>
-    <t>Expired</t>
+    <t>EXPIRED</t>
   </si>
   <si>
     <t>02/01/2018</t>
@@ -139,88 +151,88 @@
     <t>12/31/2020</t>
   </si>
   <si>
+    <t>Plumbing</t>
+  </si>
+  <si>
+    <t>Plumbing Contractor</t>
+  </si>
+  <si>
+    <t>Clear Water Plumbing</t>
+  </si>
+  <si>
+    <t>300 River Rd</t>
+  </si>
+  <si>
+    <t>Duluth</t>
+  </si>
+  <si>
+    <t>55802</t>
+  </si>
+  <si>
+    <t>2185550100</t>
+  </si>
+  <si>
     <t>PL000003</t>
   </si>
   <si>
-    <t>Plumbing Contractor</t>
-  </si>
-  <si>
-    <t>Clear Water Plumbing</t>
-  </si>
-  <si>
-    <t>300 River Rd</t>
-  </si>
-  <si>
-    <t>Duluth</t>
-  </si>
-  <si>
-    <t>55802</t>
-  </si>
-  <si>
-    <t>St. Louis</t>
-  </si>
-  <si>
-    <t>2185550100</t>
-  </si>
-  <si>
     <t>Suspended</t>
   </si>
   <si>
     <t>03/10/2019</t>
   </si>
   <si>
-    <t>Y</t>
+    <t>Order 2026-01</t>
+  </si>
+  <si>
+    <t>Electrical</t>
+  </si>
+  <si>
+    <t>Electrical Contractor</t>
+  </si>
+  <si>
+    <t>Bright North Electric</t>
+  </si>
+  <si>
+    <t>400 Circuit Blvd</t>
+  </si>
+  <si>
+    <t>Rochester</t>
+  </si>
+  <si>
+    <t>55901</t>
+  </si>
+  <si>
+    <t>5075550100</t>
   </si>
   <si>
     <t>EL000004</t>
   </si>
   <si>
-    <t>Electrical Contractor</t>
-  </si>
-  <si>
-    <t>Bright North Electric</t>
-  </si>
-  <si>
-    <t>400 Circuit Blvd</t>
-  </si>
-  <si>
-    <t>Rochester</t>
-  </si>
-  <si>
-    <t>55901</t>
-  </si>
-  <si>
-    <t>Olmsted</t>
-  </si>
-  <si>
-    <t>5075550100</t>
-  </si>
-  <si>
     <t>04/20/2021</t>
   </si>
   <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>Contractor Registration</t>
+  </si>
+  <si>
+    <t>Independent Repair Services</t>
+  </si>
+  <si>
+    <t>500 Rural Route</t>
+  </si>
+  <si>
+    <t>Bemidji</t>
+  </si>
+  <si>
+    <t>56601</t>
+  </si>
+  <si>
+    <t>2185550111</t>
+  </si>
+  <si>
     <t>IR000005</t>
-  </si>
-  <si>
-    <t>Contractor Registration</t>
-  </si>
-  <si>
-    <t>Independent Repair Services</t>
-  </si>
-  <si>
-    <t>500 Rural Route</t>
-  </si>
-  <si>
-    <t>Bemidji</t>
-  </si>
-  <si>
-    <t>56601</t>
-  </si>
-  <si>
-    <t>Beltrami</t>
-  </si>
-  <si>
-    <t>2185550111</t>
   </si>
   <si>
     <t>05/05/2022</t>
@@ -609,10 +621,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -658,287 +670,350 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N4" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>56</v>
+      </c>
+      <c r="R4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" t="s">
+        <v>65</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" t="s">
+        <v>72</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" t="s">
+        <v>73</v>
+      </c>
+      <c r="N6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+      <c r="I7" t="s">
         <v>26</v>
       </c>
-      <c r="N2" t="s">
+      <c r="J7" t="s">
         <v>27</v>
       </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="K7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="N7" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+      <c r="O7" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
+      <c r="P7" t="s">
         <v>32</v>
       </c>
-      <c r="E3" t="s">
+      <c r="Q7" t="s">
         <v>33</v>
       </c>
-      <c r="F3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" t="s">
-        <v>41</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" t="s">
-        <v>51</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" t="s">
-        <v>61</v>
-      </c>
-      <c r="N5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6" t="s">
-        <v>69</v>
-      </c>
-      <c r="L6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" t="s">
-        <v>70</v>
-      </c>
-      <c r="N6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" t="s">
-        <v>73</v>
-      </c>
-      <c r="L7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" t="s">
-        <v>28</v>
+      <c r="R7" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
